--- a/data/baidu/china_music.xlsx
+++ b/data/baidu/china_music.xlsx
@@ -580,24 +580,30 @@
           <t>https://movie.douban.com/subject/27060077/</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>49619.57142857143</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>绿皮书</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>绿皮书</t>
+        </is>
+      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +666,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -734,24 +748,30 @@
           <t>https://movie.douban.com/subject/10831445/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>2642.714285714286</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>百鸟朝凤</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>百鸟朝凤</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -814,16 +834,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>不能说的秘密</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>不能说的秘密</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -891,16 +919,24 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>丝路花雨</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>丝路花雨</t>
+        </is>
+      </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
@@ -968,16 +1004,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>黄土地</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>黄土地</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
@@ -1045,16 +1089,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>BEYOND日记之莫欺少年穷</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>BEYOND日记之莫欺少年穷</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1122,16 +1174,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>左右情缘</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>左右情缘</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1199,16 +1259,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>夜半歌声</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>夜半歌声</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1276,16 +1344,24 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>和你在一起</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>和你在一起</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
@@ -1353,16 +1429,24 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>三笑</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>三笑</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
@@ -1427,24 +1511,30 @@
           <t>https://movie.douban.com/subject/26790961/</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>10776.57142857143</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>闪光少女</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>闪光少女</t>
+        </is>
+      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1507,16 +1597,24 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>北京乐与路</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>北京乐与路</t>
+        </is>
+      </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
@@ -1580,16 +1678,24 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>捕鸟记</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>捕鸟记</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
@@ -1657,16 +1763,24 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4169292495, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>TME Live 「想你 张国荣」线上音乐会</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>TME Live 「想你 张国荣」线上音乐会</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -1734,16 +1848,24 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>洪湖赤卫队</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>洪湖赤卫队</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
@@ -1808,24 +1930,30 @@
           <t>https://movie.douban.com/subject/4842877/</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>6564.142857142857</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>蓝色骨头</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>蓝色骨头</t>
+        </is>
+      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1885,24 +2013,30 @@
           <t>https://movie.douban.com/subject/25749813/</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>8950.857142857143</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>摇滚藏獒</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>摇滚藏獒</t>
+        </is>
+      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1962,24 +2096,30 @@
           <t>https://movie.douban.com/subject/30176790/</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>28709.42857142857</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>梅艳芳</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>梅艳芳</t>
+        </is>
+      </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2042,16 +2182,24 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>红色娘子军</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>红色娘子军</t>
+        </is>
+      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -2119,16 +2267,24 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>四大天王</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>四大天王</t>
+        </is>
+      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -2193,24 +2349,30 @@
           <t>https://movie.douban.com/subject/26926321/</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>13081.42857142857</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>缝纫机乐队</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>缝纫机乐队</t>
+        </is>
+      </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2273,16 +2435,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1983年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1983年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2350,16 +2520,24 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>惊情</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>惊情</t>
+        </is>
+      </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
@@ -2424,24 +2602,30 @@
           <t>https://movie.douban.com/subject/20388242/</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>2028.714285714286</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>怒放之青春再见</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>怒放之青春再见</t>
+        </is>
+      </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -2504,16 +2688,24 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>乐队</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>乐队</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -2578,24 +2770,30 @@
           <t>https://movie.douban.com/subject/6126445/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>352.5714285714286</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>郎在对门唱山歌</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>郎在对门唱山歌</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2655,24 +2853,30 @@
           <t>https://movie.douban.com/subject/6126441/</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1763.714285714286</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>岁月无声</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>岁月无声</t>
+        </is>
+      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -2732,24 +2936,30 @@
           <t>https://movie.douban.com/subject/27041519/</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>605.1428571428571</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>哀乐女子天团</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>哀乐女子天团</t>
+        </is>
+      </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2812,16 +3022,24 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1998年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1998年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
@@ -2889,16 +3107,24 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>生活的颤音</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>生活的颤音</t>
+        </is>
+      </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
@@ -2966,16 +3192,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4172093153, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>听见歌 再唱</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>听见歌 再唱</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
@@ -3043,16 +3277,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1999年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1999年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3117,24 +3359,30 @@
           <t>https://movie.douban.com/subject/26733890/</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>1465.857142857143</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>元宵喜乐会</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>元宵喜乐会</t>
+        </is>
+      </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3194,24 +3442,30 @@
           <t>https://movie.douban.com/subject/35044539/</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>9263</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>梅艳芳·10·思念·音乐·会</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>梅艳芳</t>
+        </is>
+      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3274,16 +3528,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2009年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2009年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3351,16 +3613,24 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1984年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1984年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
@@ -3428,16 +3698,24 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>莫文蔚：好莫文蔚巡回演唱</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>莫文蔚</t>
+        </is>
+      </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
@@ -3505,16 +3783,24 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4173013803, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2020年央视中秋晚会‎</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2020年央视中秋晚会‎</t>
+        </is>
+      </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
@@ -3579,24 +3865,30 @@
           <t>https://movie.douban.com/subject/20422192/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>348</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>阆中之恋</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>阆中之恋</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3659,16 +3951,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2000年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2000年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3736,16 +4036,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>云门舞集 - 流浪者之歌</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>云门舞集</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3813,16 +4121,24 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2005年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2005年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
@@ -3887,24 +4203,30 @@
           <t>https://movie.douban.com/subject/26890949/</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>276.8571428571428</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>小戏骨：补锅</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -3967,16 +4289,24 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>爱情任务</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>爱情任务</t>
+        </is>
+      </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
@@ -4044,16 +4374,24 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2008年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2008年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
@@ -4121,16 +4459,24 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>混混天团</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>混混天团</t>
+        </is>
+      </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -4198,16 +4544,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4173846348, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17th音乐会</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>17th音乐会</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4275,16 +4629,24 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1990年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1990年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -4352,16 +4714,24 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1995年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1995年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
@@ -4429,16 +4799,24 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2001年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2001年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
@@ -4506,16 +4884,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>别恋</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>别恋</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4583,16 +4969,24 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>恋爱初歌</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>恋爱初歌</t>
+        </is>
+      </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -4657,24 +5051,30 @@
           <t>https://movie.douban.com/subject/6068517/</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>1738.571428571429</v>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>华丽之后</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>华丽之后</t>
+        </is>
+      </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -4734,24 +5134,30 @@
           <t>https://movie.douban.com/subject/26594013/</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>539.7142857142857</v>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2014年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2014年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -4814,16 +5220,24 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1996年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1996年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
@@ -4891,16 +5305,24 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>红军不怕远征难——长征组歌</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>红军不怕远征难</t>
+        </is>
+      </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
@@ -4968,16 +5390,24 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2010年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2010年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -5042,24 +5472,30 @@
           <t>https://movie.douban.com/subject/26891306/</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>328.8571428571428</v>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>小戏骨：白毛女</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -5122,16 +5558,24 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2002年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2002年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -5199,16 +5643,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1997年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1997年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5273,24 +5725,30 @@
           <t>https://movie.douban.com/subject/26594010/</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>488.8571428571428</v>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2013年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2013年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -5353,16 +5811,24 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2006年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2006年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T64" t="n">
         <v>0</v>
       </c>
@@ -5430,16 +5896,24 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>摇滚青年</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>摇滚青年</t>
+        </is>
+      </c>
       <c r="T65" t="n">
         <v>0</v>
       </c>
@@ -5507,16 +5981,24 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2003年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2003年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -5581,24 +6063,30 @@
           <t>https://movie.douban.com/subject/26594009/</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>372.8571428571428</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2012年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2012年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -5661,16 +6149,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1993年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1993年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5738,16 +6234,24 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1989年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1989年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
@@ -5815,16 +6319,24 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>冈拉梅朵</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>冈拉梅朵</t>
+        </is>
+      </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -5892,16 +6404,24 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>花木兰</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>花木兰</t>
+        </is>
+      </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
@@ -5969,16 +6489,24 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2004年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>2004年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T72" t="n">
         <v>0</v>
       </c>
@@ -6046,16 +6574,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1986年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1986年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6120,24 +6656,30 @@
           <t>https://movie.douban.com/subject/20451471/</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>3934.428571428572</v>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>听见下雨的声音</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>听见下雨的声音</t>
+        </is>
+      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -6200,16 +6742,24 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>暗恋映像</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>暗恋映像</t>
+        </is>
+      </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
@@ -6274,24 +6824,30 @@
           <t>https://movie.douban.com/subject/7055667/</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>350.7142857142857</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>起势摇滚</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>起势摇滚</t>
+        </is>
+      </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -6354,16 +6910,24 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1992年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1992年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -6431,16 +6995,24 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>宝莲灯</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>宝莲灯</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>0</v>
       </c>
@@ -6508,16 +7080,24 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2007年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2007年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -6585,16 +7165,24 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1987年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1987年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T80" t="n">
         <v>0</v>
       </c>
@@ -6659,24 +7247,30 @@
           <t>https://movie.douban.com/subject/26594007/</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>569.4285714285714</v>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2011年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>2011年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -6739,16 +7333,24 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1991年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1991年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T82" t="n">
         <v>0</v>
       </c>
@@ -6816,16 +7418,24 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4176659381, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>空气中的视听与幻觉 Live</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>空气中的视听与幻觉 Live</t>
+        </is>
+      </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
@@ -6893,16 +7503,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1988年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1988年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -6970,16 +7588,24 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>练·恋·舞</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>练·恋·舞</t>
+        </is>
+      </c>
       <c r="T85" t="n">
         <v>0</v>
       </c>
@@ -7047,16 +7673,24 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4176919362, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>大乐师．为爱配乐</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>大乐师．为爱配乐</t>
+        </is>
+      </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
@@ -7124,16 +7758,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1994年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1994年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7201,16 +7843,24 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1985年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1985年中央电视台春节联欢晚会</t>
+        </is>
+      </c>
       <c r="T88" t="n">
         <v>0</v>
       </c>
@@ -7275,24 +7925,30 @@
           <t>https://movie.douban.com/subject/27602185/</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>376.7142857142857</v>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>再见路星河</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>再见路星河</t>
+        </is>
+      </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -7355,16 +8011,24 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>开心哆来咪</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>开心哆来咪</t>
+        </is>
+      </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -7429,24 +8093,30 @@
           <t>https://movie.douban.com/subject/26890963/</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>248.7142857142857</v>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>小戏骨：三笑寻亲记</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>小戏骨</t>
+        </is>
+      </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -7509,16 +8179,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4177723239, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>4拍4家族</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>4拍4家族</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7586,16 +8264,24 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>胡同里的波西米亚人</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>胡同里的波西米亚人</t>
+        </is>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7663,16 +8349,24 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>寻找刘三姐</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>寻找刘三姐</t>
+        </is>
+      </c>
       <c r="T94" t="n">
         <v>0</v>
       </c>
@@ -7737,24 +8431,30 @@
           <t>https://movie.douban.com/subject/27620588/</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>1938.428571428571</v>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2017国剧盛典</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>2017国剧盛典</t>
+        </is>
+      </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -7814,24 +8514,30 @@
           <t>https://movie.douban.com/subject/5319823/</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>1039.857142857143</v>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>幸福卡片</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>幸福卡片</t>
+        </is>
+      </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -7894,16 +8600,24 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>诺日吉玛</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>诺日吉玛</t>
+        </is>
+      </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
@@ -7971,16 +8685,24 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>果</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>果</t>
+        </is>
+      </c>
       <c r="T98" t="n">
         <v>0</v>
       </c>
@@ -8048,16 +8770,24 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4178560445, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>梦圆东方2017东方卫视跨年盛典</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>梦圆东方2017东方卫视跨年盛典</t>
+        </is>
+      </c>
       <c r="T99" t="n">
         <v>0</v>
       </c>
@@ -8125,16 +8855,24 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>盛糖乐队</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>盛糖乐队</t>
+        </is>
+      </c>
       <c r="T100" t="n">
         <v>0</v>
       </c>
@@ -8202,16 +8940,24 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>他与罗耶戴尔</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>他与罗耶戴尔</t>
+        </is>
+      </c>
       <c r="T101" t="n">
         <v>0</v>
       </c>
@@ -8276,24 +9022,30 @@
           <t>https://movie.douban.com/subject/26985916/</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>4223.428571428572</v>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>你美丽了我的人生</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>你美丽了我的人生</t>
+        </is>
+      </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -8356,16 +9108,24 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4179100400, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>摇滚乐杀人事件</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>摇滚乐杀人事件</t>
+        </is>
+      </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
@@ -8433,16 +9193,24 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4179343162, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>“坏小子”乐团</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>“坏小子”乐团</t>
+        </is>
+      </c>
       <c r="T104" t="n">
         <v>0</v>
       </c>
@@ -8507,24 +9275,30 @@
           <t>https://movie.douban.com/subject/25706778/</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>17303.57142857143</v>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>摇滚英雄</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>摇滚英雄</t>
+        </is>
+      </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -8587,16 +9361,24 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>变幻的年代</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>变幻的年代</t>
+        </is>
+      </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
@@ -8661,21 +9443,27 @@
           <t>https://movie.douban.com/subject/35657302/</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>你是我的一束光</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>你是我的一束光</t>
+        </is>
+      </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -8738,24 +9526,30 @@
           <t>https://movie.douban.com/subject/26921076/</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>2771.571428571428</v>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>舞出我人生之舞所不能</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>舞出我人生之舞所不能</t>
+        </is>
+      </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -8818,16 +9612,24 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 4180482110, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>2016年中央电视台元宵晚会</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>2016年中央电视台元宵晚会</t>
+        </is>
+      </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
@@ -8892,24 +9694,30 @@
           <t>https://movie.douban.com/subject/6971298/</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>251.8571428571429</v>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>温哥华酱油乐队</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>温哥华酱油乐队</t>
+        </is>
+      </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -8969,24 +9777,30 @@
           <t>https://movie.douban.com/subject/6068516/</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>23957.42857142857</v>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>东成西就2011</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>东成西就2011</t>
+        </is>
+      </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -9046,24 +9860,30 @@
           <t>https://movie.douban.com/subject/10759842/</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>12307.85714285714</v>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>毕业那年</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>毕业那年</t>
+        </is>
+      </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -9123,24 +9943,30 @@
           <t>https://movie.douban.com/subject/5161713/</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr"/>
+      <c r="O113" t="n">
+        <v>610.5714285714286</v>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>梦幻飞琴</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>梦幻飞琴</t>
+        </is>
+      </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -9200,24 +10026,30 @@
           <t>https://movie.douban.com/subject/25919327/</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
+      <c r="O114" t="n">
+        <v>5208.714285714285</v>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>摇滚水果</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>摇滚水果</t>
+        </is>
+      </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -9277,24 +10109,30 @@
           <t>https://movie.douban.com/subject/6755902/</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
+      <c r="O115" t="n">
+        <v>1522.714285714286</v>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>一夜成名</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>一夜成名</t>
+        </is>
+      </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -9354,24 +10192,30 @@
           <t>https://movie.douban.com/subject/25741108/</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
+      <c r="O116" t="n">
+        <v>2748.714285714286</v>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>中国好声音之为你转身</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>中国好声音之为你转身</t>
+        </is>
+      </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
